--- a/生成AI定着ワークショップ_ワーク①.xlsx
+++ b/生成AI定着ワークショップ_ワーク①.xlsx
@@ -22,9 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="85">
-  <si>
-    <t>生成AI定着ワークショップ　サンプルデータ集</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="85">
+  <si>
+    <t>生成AI定着ワークショップ　ワーク①シート</t>
   </si>
   <si>
     <t>2026年9月29日（火）／ STYLE ARTS Inc.</t>
@@ -33,13 +33,13 @@
     <t>このファイルについて</t>
   </si>
   <si>
-    <t>当日のワークで使えるサンプルデータをまとめています。各ワークに3種類ずつ用意しているので、ご自身の業務に近いものを選んでお使いください。</t>
-  </si>
-  <si>
-    <t>すべて架空のデータです。実在の商品・店舗・人物とは関係ありません。</t>
-  </si>
-  <si>
-    <t>ご自身のデータを使う場合</t>
+    <t>ワーク①「業務課題の棚卸し」で使うシートと記入例です。記入例は、ご自身の業務に近いものを参考にしてください。</t>
+  </si>
+  <si>
+    <t>記入例はすべて架空のものです。実在の商品・店舗・人物とは関係ありません。</t>
+  </si>
+  <si>
+    <t>ご自身のデータをAIに入力する場合</t>
   </si>
   <si>
     <t>店頭やWebですでに公開している情報に限ってお使いください。</t>
@@ -51,7 +51,7 @@
     <t>入力しない例：お客様の氏名・連絡先・査定内容、従業員の個人情報、仕入原価、取引先との契約条件、未公表の売上データ</t>
   </si>
   <si>
-    <t>迷ったら、このファイルのサンプルデータをお使いください。</t>
+    <t>迷ったときは、「〇〇」などに置き換えてから入力しましょう。</t>
   </si>
   <si>
     <t>シートの一覧</t>
@@ -75,7 +75,7 @@
     <t>ワーク①　業務課題の棚卸しシート</t>
   </si>
   <si>
-    <t>1日の業務を書き出し、AIに任せられそうな工程を見つけます。※ 色つきの行は記入例です。2行目以降にご自身の業務を記入してください。</t>
+    <t>1日の業務を書き出し、AIに任せられそうな工程を見つけます。※ 色つきの行は記入例です。その下の行から、ご自身の業務を記入してください。</t>
   </si>
   <si>
     <t>時間帯</t>
@@ -708,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="130" customWidth="1"/>
@@ -781,26 +781,6 @@
     <row r="15" spans="1:1" ht="16.5">
       <c r="A15" s="3" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="16.5">
-      <c r="A16" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="16.5">
-      <c r="A17" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="16.5">
-      <c r="A18" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="16.5">
-      <c r="A19" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
